--- a/artfynd/A 44323-2021 artfynd.xlsx
+++ b/artfynd/A 44323-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44323-2021 artfynd.xlsx
+++ b/artfynd/A 44323-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113255185</v>
+        <v>113255183</v>
       </c>
       <c r="B2" t="n">
-        <v>97628</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>3674</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>stenkumla kube, Gtl</t>
+          <t>Stenkumla Kube, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>694933</v>
+        <v>694943</v>
       </c>
       <c r="R2" t="n">
-        <v>6383158</v>
+        <v>6383164</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113255181</v>
+        <v>116967099</v>
       </c>
       <c r="B3" t="n">
-        <v>86193</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58085</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,37 +787,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>249228</v>
+        <v>205976</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stenkumla Kube, Gtl</t>
+          <t>Kubemyr, Kubemyr, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>695011</v>
+        <v>694937</v>
       </c>
       <c r="R3" t="n">
-        <v>6383149</v>
+        <v>6383166</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,12 +855,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flög upp ur skogen och möte oroligt kraxande en korp som flög förbi.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,19 +884,18 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Amanda Overmark</t>
+          <t>Fredrik Gustafsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Amanda Overmark</t>
+          <t>Fredrik Gustafsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -891,12 +905,7 @@
         <v>113255178</v>
       </c>
       <c r="B4" t="n">
-        <v>97628</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,15 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113255183</v>
+        <v>113255185</v>
       </c>
       <c r="B5" t="n">
-        <v>86180</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,37 +1015,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3674</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stenkumla Kube, Gtl</t>
+          <t>stenkumla kube, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>694943</v>
+        <v>694933</v>
       </c>
       <c r="R5" t="n">
-        <v>6383164</v>
+        <v>6383158</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,6 +1103,107 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>113255181</v>
+      </c>
+      <c r="B6" t="n">
+        <v>87323</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>249228</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Barrfagerspindling</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cortinarius piceae</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stenkumla Kube, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>695011</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6383149</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stenkumla</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-11-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-11-14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Amanda Overmark</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Amanda Overmark</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44323-2021 artfynd.xlsx
+++ b/artfynd/A 44323-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113255183</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116967099</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113255178</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,6 +1123,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113255185</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,8 +1229,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113255181</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>